--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table127.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table127.xlsx
@@ -82,8 +82,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="d\-mmmm\-yyyy"/>
-    <numFmt numFmtId="169" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="d\-mmmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -129,7 +129,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,12 +145,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,7 +219,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -233,69 +227,69 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,82 +772,82 @@
   <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:10" ht="20">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="13"/>
+      <c r="E1" s="18"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:10" ht="20">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="14">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20">
         <v>41884</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="11" t="s">
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -986,10 +980,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="4">
         <v>16</v>
       </c>
@@ -1006,10 +1000,10 @@
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="20"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="6">
         <v>-16</v>
       </c>
